--- a/sample_data/sample_invoices.xlsx
+++ b/sample_data/sample_invoices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,11 @@
           <t>remarks</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>order_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -480,17 +485,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bright Medical Trading Ltd</t>
+          <t>Victoria Harbour Eye Institute</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46112</v>
+        <v>46053</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46142</v>
+        <v>46083</v>
       </c>
       <c r="E2" t="n">
-        <v>58000</v>
+        <v>68000</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -512,7 +517,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Awaiting wire confirmation</t>
+          <t>Awaiting wire confirmation from finance</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SO-2026-001</t>
         </is>
       </c>
     </row>
@@ -524,37 +534,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Silver Oak Supplies</t>
+          <t>Kowloon Central Hospital</t>
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46152</v>
+        <v>46158</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="E3" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Unpaid</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SO-2026-004</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -564,20 +579,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tai Yick Trading Co</t>
+          <t>Lion Rock Vision Clinic Group</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46137</v>
+        <v>46193</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46167</v>
+        <v>46223</v>
       </c>
       <c r="E4" t="n">
-        <v>9000</v>
+        <v>9600</v>
       </c>
       <c r="F4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -586,17 +601,18 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Unpaid</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jesse</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Partial payment received, balance pending</t>
+          <t>Marcus</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SO-2026-007</t>
         </is>
       </c>
     </row>
@@ -608,37 +624,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Formosa Industrial Group</t>
+          <t>Harbour City Biomedical Services</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46172</v>
+        <v>46198</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="E5" t="n">
-        <v>15000</v>
+        <v>4200</v>
       </c>
       <c r="F5" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Unpaid</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Marcus</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Wendy</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Confirm PO before due date</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SO-2026-010</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -648,20 +673,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Golden Harbor Logistics</t>
+          <t>New Territories Optical Supplies</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46192</v>
+        <v>46173</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46227</v>
+        <v>46201</v>
       </c>
       <c r="E6" t="n">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -670,15 +695,24 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Unpaid</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Wendy</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Jesse</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Partial payment received, balance pending</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SO-2026-012</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -688,14 +722,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lion City Retail Pte Ltd</t>
+          <t>Pearl River Medical Distribution Co</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46202</v>
+        <v>46163</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46217</v>
+        <v>46193</v>
       </c>
       <c r="E7" t="n">
         <v>18000</v>
@@ -705,7 +739,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -715,12 +749,13 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Marcus</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Confirm PO before due date</t>
+          <t>Wendy</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SO-2026-002</t>
         </is>
       </c>
     </row>
@@ -732,37 +767,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bright Medical Trading Ltd</t>
+          <t>Golden Bay Optical Chain</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46127</v>
+        <v>46148</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46157</v>
+        <v>46178</v>
       </c>
       <c r="E8" t="n">
-        <v>27000</v>
+        <v>12500</v>
       </c>
       <c r="F8" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Unpaid</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SO-2026-006</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,37 +812,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Silver Oak Supplies</t>
+          <t>Zhuhai Cross-Border Medical Center</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46177</v>
+        <v>46138</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46207</v>
+        <v>46165</v>
       </c>
       <c r="E9" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F9" t="n">
         <v>8000</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Unpaid</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SO-2026-013</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -812,27 +857,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Formosa Industrial Group</t>
+          <t>Huangpu District Eye Hospital</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>46168</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46195</v>
+      </c>
       <c r="E10" t="n">
-        <v>14000</v>
+        <v>9500</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Unpaid</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -842,7 +889,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Due date pending confirmation from customer</t>
+          <t>Partial payment received, balance pending</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SO-2026-003</t>
         </is>
       </c>
     </row>
@@ -854,37 +906,813 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lion City Retail Pte Ltd</t>
+          <t>Shanghai Vision Research Institute</t>
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46197</v>
+        <v>46133</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46210</v>
+        <v>46161</v>
       </c>
       <c r="E11" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SO-2026-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INV-2026-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bund Optical Partners</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="E12" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SO-2026-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INV-2026-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Beijing Capital Eye Center</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>46103</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="E13" t="n">
+        <v>31000</v>
+      </c>
+      <c r="F13" t="n">
         <v>6000</v>
       </c>
-      <c r="F11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SGD</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SO-2026-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>INV-2026-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chaoyang Medical Equipment Co</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="E14" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SO-2026-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>INV-2026-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Northern Star University Hospital</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8700</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Marcus</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SO-2026-011</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>INV-2026-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sichuan Regional Health Distributors</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="E16" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SO-2026-015</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>INV-2026-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Yangtze Vision Clinic Network</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>High-value order, follow up urgently</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SO-2026-016</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>INV-2026-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fujian Coastal Eye Care Group</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6400</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SO-2026-017</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>INV-2026-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kowloon Central Hospital</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Confirm receipt of goods</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SO-2026-021</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>INV-2026-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Victoria Harbour Eye Institute</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5600</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SO-2026-018</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>INV-2026-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lion Rock Vision Clinic Group</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>SO-2026-023</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>INV-2026-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Golden Bay Optical Chain</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9800</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>SO-2026-024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>INV-2026-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Chaoyang Medical Equipment Co</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15300</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>SO-2026-025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>INV-2026-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Northern Star University Hospital</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46123</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8900</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>SO-2026-026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>INV-2026-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Shanghai Vision Research Institute</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>11200</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Due date pending confirmation from customer</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SO-2026-027</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>INV-2026-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bund Optical Partners</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-500</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Amount under review — possible entry error</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>INV-2026-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Beijing Capital Eye Center</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Overpayment recorded — refund or credit pending finance review</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INV-2026-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sichuan Regional Health Distributors</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16400</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
